--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.79926175692756</v>
+        <v>5.654880035500729</v>
       </c>
       <c r="D2" t="n">
-        <v>56.62562587159381</v>
+        <v>9.201664204133994</v>
       </c>
       <c r="E2" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F2" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.52979915417761</v>
+        <v>1.711092362553862</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6706154486855</v>
+        <v>5.471475010411394</v>
       </c>
       <c r="E3" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F3" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.787977963012063</v>
+        <v>1.59054641898946</v>
       </c>
       <c r="D4" t="n">
-        <v>12.10517287690497</v>
+        <v>1.967090592497058</v>
       </c>
       <c r="E4" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F4" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.72736221634896</v>
+        <v>5.480696360156707</v>
       </c>
       <c r="D5" t="n">
-        <v>31.41935401253486</v>
+        <v>5.105645027036914</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F5" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.0440872622193</v>
+        <v>4.232164180110637</v>
       </c>
       <c r="D6" t="n">
-        <v>26.80184580740002</v>
+        <v>4.355299943702504</v>
       </c>
       <c r="E6" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F6" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.08884158806782</v>
+        <v>7.81443675806102</v>
       </c>
       <c r="D7" t="n">
-        <v>46.99285188849046</v>
+        <v>7.636338431879699</v>
       </c>
       <c r="E7" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F7" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.16893392777813</v>
+        <v>7.502451763263947</v>
       </c>
       <c r="D8" t="n">
-        <v>47.65382666944453</v>
+        <v>7.743746833784737</v>
       </c>
       <c r="E8" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F8" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.52862038204621</v>
+        <v>6.58590081208251</v>
       </c>
       <c r="D9" t="n">
-        <v>46.74457225806712</v>
+        <v>7.595992991935907</v>
       </c>
       <c r="E9" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.89117652699723</v>
+        <v>7.294816185637051</v>
       </c>
       <c r="D10" t="n">
-        <v>49.71425318517249</v>
+        <v>8.07856614259053</v>
       </c>
       <c r="E10" t="n">
-        <v>13.72092866224373</v>
+        <v>2.229650907614606</v>
       </c>
       <c r="F10" t="n">
-        <v>13.25873726283168</v>
+        <v>2.154544805210147</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
